--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="234">
   <si>
     <t>常量键</t>
   </si>
@@ -100,7 +100,7 @@
     <t>AttackSpeed constant term</t>
   </si>
   <si>
-    <t>攻速=本值+AttackSpeedAgiDiv/max(敏捷,1)中的常数项</t>
+    <t>攻速=本值+敏捷相关项中的常数项</t>
   </si>
   <si>
     <t>AttackSpeedAgiDiv</t>
@@ -149,6 +149,591 @@
   </si>
   <si>
     <t>士兵最大生命=ceil(躯体生命+力量×本系数)</t>
+  </si>
+  <si>
+    <t>CameraHeightY</t>
+  </si>
+  <si>
+    <t>镜头高度</t>
+  </si>
+  <si>
+    <t>Top-down camera world Y above map center</t>
+  </si>
+  <si>
+    <t>俯视正交相机相对地图中心的世界Y高度；Dig/Defend/布阵/PushMap共用</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMargin</t>
+  </si>
+  <si>
+    <t>地图适配Size余量</t>
+  </si>
+  <si>
+    <t>orthoSize = max(halfExtents) - margin</t>
+  </si>
+  <si>
+    <t>Dig/Defend/布阵：正交Size=地图半幅较大边减去本余量</t>
+  </si>
+  <si>
+    <t>PushMapCameraOrthoSize</t>
+  </si>
+  <si>
+    <t>推图开战默认Size</t>
+  </si>
+  <si>
+    <t>PushMap combat default orthographicSize</t>
+  </si>
+  <si>
+    <t>PushMap开战默认正交Size（异于Defend的地图适配公式）</t>
+  </si>
+  <si>
+    <t>CameraNearClip</t>
+  </si>
+  <si>
+    <t>镜头近裁剪面</t>
+  </si>
+  <si>
+    <t>Camera nearClipPlane</t>
+  </si>
+  <si>
+    <t>正交相机近裁剪面</t>
+  </si>
+  <si>
+    <t>CameraFarClip</t>
+  </si>
+  <si>
+    <t>镜头远裁剪面</t>
+  </si>
+  <si>
+    <t>Camera farClipPlane</t>
+  </si>
+  <si>
+    <t>正交相机远裁剪面</t>
+  </si>
+  <si>
+    <t>CameraFollowDeadzone</t>
+  </si>
+  <si>
+    <t>跟随死区半径</t>
+  </si>
+  <si>
+    <t>PushMap Auto follow deadzone world-XZ</t>
+  </si>
+  <si>
+    <t>PushMap Auto跟随：目标在死区内则镜头XZ不移动</t>
+  </si>
+  <si>
+    <t>CameraFollowSmoothTime</t>
+  </si>
+  <si>
+    <t>跟随平滑时间</t>
+  </si>
+  <si>
+    <t>PushMap Auto SmoothDamp time</t>
+  </si>
+  <si>
+    <t>PushMap Auto跟随：超出死区后XZ SmoothDamp时间（秒）</t>
+  </si>
+  <si>
+    <t>CameraZoomStepPerNotch</t>
+  </si>
+  <si>
+    <t>滚轮缩放步进</t>
+  </si>
+  <si>
+    <t>Scroll wheel orthographicSize step</t>
+  </si>
+  <si>
+    <t>PushMap滚轮每格改变的正交Size</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMin</t>
+  </si>
+  <si>
+    <t>正交Size下限</t>
+  </si>
+  <si>
+    <t>Min orthographicSize clamp</t>
+  </si>
+  <si>
+    <t>正交Size下限（含Dig/Defend适配结果钳制与PushMap缩放）</t>
+  </si>
+  <si>
+    <t>CameraOrthoSizeMax</t>
+  </si>
+  <si>
+    <t>正交Size上限</t>
+  </si>
+  <si>
+    <t>Max orthographicSize clamp</t>
+  </si>
+  <si>
+    <t>PushMap滚轮缩放上限</t>
+  </si>
+  <si>
+    <t>CameraDragThresholdPixels</t>
+  </si>
+  <si>
+    <t>拖拽启动像素阈值</t>
+  </si>
+  <si>
+    <t>LMB drag arm threshold in screen px</t>
+  </si>
+  <si>
+    <t>PushMap手动拖镜头：累计位移超过本像素才开始平移</t>
+  </si>
+  <si>
+    <t>PushMapCameraIntroSpeed</t>
+  </si>
+  <si>
+    <t>推图镜头预览速度</t>
+  </si>
+  <si>
+    <t>PushMap StartBattle Intro rail speed world-XZ units/sec</t>
+  </si>
+  <si>
+    <t>PushMap开战镜头预览沿CameraFollowPath的世界XZ恒速（单位/秒）</t>
+  </si>
+  <si>
+    <t>PushMapCameraIntroWaypointDwellSeconds</t>
+  </si>
+  <si>
+    <t>推图镜头预览路点停留</t>
+  </si>
+  <si>
+    <t>PushMap Intro dwell seconds at each author WP</t>
+  </si>
+  <si>
+    <t>PushMap开战镜头预览在每个作者路点（含起终点）的停留秒数</t>
+  </si>
+  <si>
+    <t>DigTriggerDwellSeconds</t>
+  </si>
+  <si>
+    <t>挖坟触发停留</t>
+  </si>
+  <si>
+    <t>Cursor dwell before DigAction starts</t>
+  </si>
+  <si>
+    <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+  </si>
+  <si>
+    <t>BaseDigDuration</t>
+  </si>
+  <si>
+    <t>挖坟基础时长</t>
+  </si>
+  <si>
+    <t>BaseDigDuration seconds</t>
+  </si>
+  <si>
+    <t>DigActionDuration=max(下限</t>
+  </si>
+  <si>
+    <t>DigActionDurationFloor</t>
+  </si>
+  <si>
+    <t>挖坟最短时长</t>
+  </si>
+  <si>
+    <t>Min DigActionDuration seconds</t>
+  </si>
+  <si>
+    <t>单次挖坟最短秒数（公式地板）</t>
+  </si>
+  <si>
+    <t>AttackSlotMeleeCount</t>
+  </si>
+  <si>
+    <t>近战攻击位数量</t>
+  </si>
+  <si>
+    <t>Melee AttackSlot ring slot count</t>
+  </si>
+  <si>
+    <t>近战单位围绕目标可占用的攻击位数量</t>
+  </si>
+  <si>
+    <t>AttackSlotRangedCount</t>
+  </si>
+  <si>
+    <t>远程攻击位数量</t>
+  </si>
+  <si>
+    <t>Ranged AttackSlot ring slot count</t>
+  </si>
+  <si>
+    <t>远程单位围绕目标可占用的攻击位数量</t>
+  </si>
+  <si>
+    <t>AttackSlotMargin</t>
+  </si>
+  <si>
+    <t>攻击位环半径余量</t>
+  </si>
+  <si>
+    <t>Ring radius = reach sum - margin</t>
+  </si>
+  <si>
+    <t>攻击位环半径计算时从可达距离减去的余量</t>
+  </si>
+  <si>
+    <t>AttackSlotMinRingRadius</t>
+  </si>
+  <si>
+    <t>攻击位环最小半径</t>
+  </si>
+  <si>
+    <t>Min AttackSlot ring radius</t>
+  </si>
+  <si>
+    <t>攻击位环半径下限</t>
+  </si>
+  <si>
+    <t>AttackSlotReclaimMoveThreshold</t>
+  </si>
+  <si>
+    <t>攻击位重算位移阈值</t>
+  </si>
+  <si>
+    <t>Target move distance to recompute slots</t>
+  </si>
+  <si>
+    <t>目标移动超过本距离时重算攻击位</t>
+  </si>
+  <si>
+    <t>AttackSlotDefaultTargetBodyRadius</t>
+  </si>
+  <si>
+    <t>默认目标体半径</t>
+  </si>
+  <si>
+    <t>Fallback target BodyRadius</t>
+  </si>
+  <si>
+    <t>缺体外观/怪物半径时的默认目标体半径</t>
+  </si>
+  <si>
+    <t>HitConfirmSlack</t>
+  </si>
+  <si>
+    <t>命中确认松弛距离</t>
+  </si>
+  <si>
+    <t>HitConfirm range slack</t>
+  </si>
+  <si>
+    <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+  </si>
+  <si>
+    <t>SurroundGapDegrees</t>
+  </si>
+  <si>
+    <t>包围缺口角度</t>
+  </si>
+  <si>
+    <t>Surround gap sector degrees</t>
+  </si>
+  <si>
+    <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+  </si>
+  <si>
+    <t>StuckDetectWindowSeconds</t>
+  </si>
+  <si>
+    <t>卡死检测窗口</t>
+  </si>
+  <si>
+    <t>StuckHold detect window seconds</t>
+  </si>
+  <si>
+    <t>有移动意图但位移不足时的检测窗口秒数</t>
+  </si>
+  <si>
+    <t>StuckDisplacementEpsilon</t>
+  </si>
+  <si>
+    <t>卡死位移阈值</t>
+  </si>
+  <si>
+    <t>StuckHold displacement epsilon</t>
+  </si>
+  <si>
+    <t>检测窗口内XZ位移小于本值则判定卡住</t>
+  </si>
+  <si>
+    <t>StuckHoldSeconds</t>
+  </si>
+  <si>
+    <t>卡死停顿时长</t>
+  </si>
+  <si>
+    <t>StuckHold force-Idle seconds</t>
+  </si>
+  <si>
+    <t>判定卡住后强制Idle的秒数</t>
+  </si>
+  <si>
+    <t>ProjectileDefaultHitRadius</t>
+  </si>
+  <si>
+    <t>投射物默认命中半径</t>
+  </si>
+  <si>
+    <t>Default projectile soft-hit radius</t>
+  </si>
+  <si>
+    <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+  </si>
+  <si>
+    <t>DefendVictoryStageExp</t>
+  </si>
+  <si>
+    <t>防守胜利阶段经验</t>
+  </si>
+  <si>
+    <t>Defend victory Demo stage Exp</t>
+  </si>
+  <si>
+    <t>Defend清场胜利结算时入账的阶段经验</t>
+  </si>
+  <si>
+    <t>FlowFieldDefaultCellSize</t>
+  </si>
+  <si>
+    <t>流场默认格宽</t>
+  </si>
+  <si>
+    <t>FlowField default cell size</t>
+  </si>
+  <si>
+    <t>共享目标流场默认格子边长</t>
+  </si>
+  <si>
+    <t>FlowFieldMinCellSize</t>
+  </si>
+  <si>
+    <t>流场最小格宽</t>
+  </si>
+  <si>
+    <t>FlowField min cell size</t>
+  </si>
+  <si>
+    <t>流场格宽下限（性能降级时可抬高）</t>
+  </si>
+  <si>
+    <t>FlowFieldMaxCellSize</t>
+  </si>
+  <si>
+    <t>流场最大格宽</t>
+  </si>
+  <si>
+    <t>FlowField max cell size</t>
+  </si>
+  <si>
+    <t>流场格宽上限</t>
+  </si>
+  <si>
+    <t>MassMoveMaxRecalcPerFrame</t>
+  </si>
+  <si>
+    <t>群体移动每帧重算上限</t>
+  </si>
+  <si>
+    <t>MassMove/AttackSlot refresh budget per frame</t>
+  </si>
+  <si>
+    <t>每帧最多重算路径/攻击位的单位数</t>
+  </si>
+  <si>
+    <t>MassMoveDefaultAgentRadius</t>
+  </si>
+  <si>
+    <t>群体移动默认体半径</t>
+  </si>
+  <si>
+    <t>Default mass-move agent radius</t>
+  </si>
+  <si>
+    <t>群体移动登记时的默认体半径</t>
+  </si>
+  <si>
+    <t>MassMoveArriveEpsilon</t>
+  </si>
+  <si>
+    <t>群体移动到达阈值</t>
+  </si>
+  <si>
+    <t>Arrive epsilon for DesiredDestination</t>
+  </si>
+  <si>
+    <t>到达期望点判定的距离阈值</t>
+  </si>
+  <si>
+    <t>MassMoveDefaultObjectiveArriveRadius</t>
+  </si>
+  <si>
+    <t>目标到达默认半径</t>
+  </si>
+  <si>
+    <t>Default Objective arrive radius</t>
+  </si>
+  <si>
+    <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+  </si>
+  <si>
+    <t>MassMoveAttackSlotSeparationScale</t>
+  </si>
+  <si>
+    <t>攻击位软分离系数</t>
+  </si>
+  <si>
+    <t>LocalDetour separation scale in AttackSlot</t>
+  </si>
+  <si>
+    <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+  </si>
+  <si>
+    <t>SoftCollisionMaxCorrectionSpeed</t>
+  </si>
+  <si>
+    <t>软碰撞最大修正速度</t>
+  </si>
+  <si>
+    <t>Soft collision max correction speed</t>
+  </si>
+  <si>
+    <t>软碰撞位置修正速度上限（单位/秒）</t>
+  </si>
+  <si>
+    <t>LocalDetourProbeLength</t>
+  </si>
+  <si>
+    <t>本地绕行探测长度</t>
+  </si>
+  <si>
+    <t>LocalDetour L/R probe length</t>
+  </si>
+  <si>
+    <t>左右绕行探测射线长度</t>
+  </si>
+  <si>
+    <t>LocalDetourSoftSeparationStrength</t>
+  </si>
+  <si>
+    <t>本地绕行软分离强度</t>
+  </si>
+  <si>
+    <t>LocalDetour soft separation strength</t>
+  </si>
+  <si>
+    <t>友军软分离推力强度</t>
+  </si>
+  <si>
+    <t>LocalDetourDetourBias</t>
+  </si>
+  <si>
+    <t>本地绕行偏置</t>
+  </si>
+  <si>
+    <t>LocalDetour L/R bias blend</t>
+  </si>
+  <si>
+    <t>绕行方向与原期望方向的混合偏置</t>
+  </si>
+  <si>
+    <t>LocalDetourForwardConeHalfAngleDeg</t>
+  </si>
+  <si>
+    <t>本地绕行前向锥半角</t>
+  </si>
+  <si>
+    <t>Forward block cone half-angle degrees</t>
+  </si>
+  <si>
+    <t>判定前方友军阻挡的圆锥半角（度）</t>
+  </si>
+  <si>
+    <t>BossAdvanceArriveRadius</t>
+  </si>
+  <si>
+    <t>Boss推进到达半径</t>
+  </si>
+  <si>
+    <t>BossPoint advance arrive radius</t>
+  </si>
+  <si>
+    <t>目标链耗尽后推进Boss点的到达半径</t>
+  </si>
+  <si>
+    <t>EngageStickHysteresisMargin</t>
+  </si>
+  <si>
+    <t>接战粘滞余量</t>
+  </si>
+  <si>
+    <t>Engage sticky retarget hysteresis</t>
+  </si>
+  <si>
+    <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+  </si>
+  <si>
+    <t>PushMapSpawnMinSampleDistance</t>
+  </si>
+  <si>
+    <t>刷怪散布最小采样距</t>
+  </si>
+  <si>
+    <t>PushMap spawn min sample distance</t>
+  </si>
+  <si>
+    <t>刷怪散布环形采样的最小间距</t>
+  </si>
+  <si>
+    <t>PushMapSpawnSampleDistanceBodyMul</t>
+  </si>
+  <si>
+    <t>刷怪散布体半径倍数</t>
+  </si>
+  <si>
+    <t>Spawn sample distance = max(min</t>
+  </si>
+  <si>
+    <t>r*mul)</t>
+  </si>
+  <si>
+    <t>PushMapSpawnLeashSlack</t>
+  </si>
+  <si>
+    <t>刷怪拴绳松弛</t>
+  </si>
+  <si>
+    <t>NavMesh sample leash slack</t>
+  </si>
+  <si>
+    <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+  </si>
+  <si>
+    <t>PushMapSpawnAbsoluteLeashFloor</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳下限</t>
+  </si>
+  <si>
+    <t>Absolute leash floor</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳距离下限</t>
+  </si>
+  <si>
+    <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+  </si>
+  <si>
+    <t>刷怪绝对拴绳体倍数</t>
+  </si>
+  <si>
+    <t>Absolute leash = max(floor</t>
   </si>
 </sst>
 </file>
@@ -161,14 +746,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,12 +899,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -626,153 +1210,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1114,12 +1701,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="20.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="32.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="42.0833333333333" customWidth="1"/>
+    <col min="1" max="1" width="21.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1156,20 +1743,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1275,8 +1862,841 @@
         <v>38</v>
       </c>
     </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11">
+        <v>1.5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>0.15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>0.25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23">
+        <v>0.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24">
+        <v>0.8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>0.1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28">
+        <v>0.05</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29">
+        <v>0.05</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31">
+        <v>0.35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32">
+        <v>0.05</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33">
+        <v>60</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37">
+        <v>0.55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39">
+        <v>0.5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40">
+        <v>0.25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41">
+        <v>0.5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42">
+        <v>50</v>
+      </c>
+      <c r="D42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43">
+        <v>0.1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44">
+        <v>0.08</v>
+      </c>
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46">
+        <v>0.35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49">
+        <v>0.15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50">
+        <v>0.85</v>
+      </c>
+      <c r="D50" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52">
+        <v>0.35</v>
+      </c>
+      <c r="D52" t="s">
+        <v>209</v>
+      </c>
+      <c r="E52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" t="s">
+        <v>212</v>
+      </c>
+      <c r="C53">
+        <v>0.15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>213</v>
+      </c>
+      <c r="E53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54">
+        <v>0.75</v>
+      </c>
+      <c r="D54" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55">
+        <v>2.5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56">
+        <v>0.35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>233</v>
+      </c>
+      <c r="E58" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1702,11 +1702,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="23.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="39.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>0.1</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="238">
   <si>
     <t>常量键</t>
   </si>
@@ -185,6 +185,18 @@
   </si>
   <si>
     <t>PushMap开战默认正交Size（异于Defend的地图适配公式）</t>
+  </si>
+  <si>
+    <t>PushMapPrepareOrthoSize</t>
+  </si>
+  <si>
+    <t>推图布阵默认Size</t>
+  </si>
+  <si>
+    <t>PushMap Prepare FormationCamera orthographicSize (not map-fit)</t>
+  </si>
+  <si>
+    <t>PushMap Prepare 布阵 FormationCamera 正交Size（不用地图适配公式）</t>
   </si>
   <si>
     <t>CameraNearClip</t>
@@ -1210,158 +1222,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1701,12 +1714,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="39.5" customWidth="1"/>
+    <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1921,7 +1934,7 @@
         <v>52</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -1938,7 +1951,7 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
@@ -1955,7 +1968,7 @@
         <v>60</v>
       </c>
       <c r="C15">
-        <v>0.15</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -1972,7 +1985,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -1989,7 +2002,7 @@
         <v>68</v>
       </c>
       <c r="C17">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D17" t="s">
         <v>69</v>
@@ -2023,7 +2036,7 @@
         <v>76</v>
       </c>
       <c r="C19">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D19" t="s">
         <v>77</v>
@@ -2040,7 +2053,7 @@
         <v>80</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -2057,7 +2070,7 @@
         <v>84</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>85</v>
@@ -2074,7 +2087,7 @@
         <v>88</v>
       </c>
       <c r="C22">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>89</v>
@@ -2091,7 +2104,7 @@
         <v>92</v>
       </c>
       <c r="C23">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -2108,7 +2121,7 @@
         <v>96</v>
       </c>
       <c r="C24">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D24" t="s">
         <v>97</v>
@@ -2125,7 +2138,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="D25" t="s">
         <v>101</v>
@@ -2142,7 +2155,7 @@
         <v>104</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="D26" t="s">
         <v>105</v>
@@ -2159,7 +2172,7 @@
         <v>108</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -2176,7 +2189,7 @@
         <v>112</v>
       </c>
       <c r="C28">
-        <v>0.05</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
         <v>113</v>
@@ -2210,7 +2223,7 @@
         <v>120</v>
       </c>
       <c r="C30">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -2227,7 +2240,7 @@
         <v>124</v>
       </c>
       <c r="C31">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -2244,7 +2257,7 @@
         <v>128</v>
       </c>
       <c r="C32">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="D32" t="s">
         <v>129</v>
@@ -2261,7 +2274,7 @@
         <v>132</v>
       </c>
       <c r="C33">
-        <v>60</v>
+        <v>0.05</v>
       </c>
       <c r="D33" t="s">
         <v>133</v>
@@ -2278,7 +2291,7 @@
         <v>136</v>
       </c>
       <c r="C34">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
         <v>137</v>
@@ -2295,7 +2308,7 @@
         <v>140</v>
       </c>
       <c r="C35">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D35" t="s">
         <v>141</v>
@@ -2312,7 +2325,7 @@
         <v>144</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -2329,7 +2342,7 @@
         <v>148</v>
       </c>
       <c r="C37">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="D37" t="s">
         <v>149</v>
@@ -2346,7 +2359,7 @@
         <v>152</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>0.55</v>
       </c>
       <c r="D38" t="s">
         <v>153</v>
@@ -2363,7 +2376,7 @@
         <v>156</v>
       </c>
       <c r="C39">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
         <v>157</v>
@@ -2380,7 +2393,7 @@
         <v>160</v>
       </c>
       <c r="C40">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D40" t="s">
         <v>161</v>
@@ -2397,7 +2410,7 @@
         <v>164</v>
       </c>
       <c r="C41">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D41" t="s">
         <v>165</v>
@@ -2414,7 +2427,7 @@
         <v>168</v>
       </c>
       <c r="C42">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D42" t="s">
         <v>169</v>
@@ -2431,7 +2444,7 @@
         <v>172</v>
       </c>
       <c r="C43">
-        <v>0.1</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
         <v>173</v>
@@ -2448,7 +2461,7 @@
         <v>176</v>
       </c>
       <c r="C44">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D44" t="s">
         <v>177</v>
@@ -2465,7 +2478,7 @@
         <v>180</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="D45" t="s">
         <v>181</v>
@@ -2482,7 +2495,7 @@
         <v>184</v>
       </c>
       <c r="C46">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
         <v>185</v>
@@ -2499,7 +2512,7 @@
         <v>188</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0.35</v>
       </c>
       <c r="D47" t="s">
         <v>189</v>
@@ -2516,7 +2529,7 @@
         <v>192</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
@@ -2533,7 +2546,7 @@
         <v>196</v>
       </c>
       <c r="C49">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
         <v>197</v>
@@ -2550,7 +2563,7 @@
         <v>200</v>
       </c>
       <c r="C50">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="D50" t="s">
         <v>201</v>
@@ -2567,7 +2580,7 @@
         <v>204</v>
       </c>
       <c r="C51">
-        <v>50</v>
+        <v>0.85</v>
       </c>
       <c r="D51" t="s">
         <v>205</v>
@@ -2584,7 +2597,7 @@
         <v>208</v>
       </c>
       <c r="C52">
-        <v>0.35</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
         <v>209</v>
@@ -2601,7 +2614,7 @@
         <v>212</v>
       </c>
       <c r="C53">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="D53" t="s">
         <v>213</v>
@@ -2618,7 +2631,7 @@
         <v>216</v>
       </c>
       <c r="C54">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="D54" t="s">
         <v>217</v>
@@ -2635,7 +2648,7 @@
         <v>220</v>
       </c>
       <c r="C55">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="D55" t="s">
         <v>221</v>
@@ -2652,7 +2665,7 @@
         <v>224</v>
       </c>
       <c r="C56">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="D56" t="s">
         <v>225</v>
@@ -2669,7 +2682,7 @@
         <v>228</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="D57" t="s">
         <v>229</v>
@@ -2686,13 +2699,30 @@
         <v>232</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" t="s">
+        <v>236</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>237</v>
+      </c>
+      <c r="E59" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="26.5" customWidth="1" style="2" min="1" max="1"/>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="C60" s="0" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>击飞距离raw=(MaxHp/OutgoingDamage)×本系数；再clamp到Min/Max</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="C61" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="C62" s="0" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
@@ -2599,6 +2599,31 @@
       <c r="E62" s="0" t="inlineStr">
         <is>
           <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>DeathDie2KnockbackThreshold</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>死亡Die2击退阈值</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <si>
     <t>常量键</t>
   </si>
@@ -163,6 +163,18 @@
     <t>俯视正交相机相对地图中心的世界Y高度；Dig/Defend/布阵/PushMap共用</t>
   </si>
   <si>
+    <t>CombatCameraPitchDegrees</t>
+  </si>
+  <si>
+    <t>战斗相机倾角</t>
+  </si>
+  <si>
+    <t>Defend+PushMap Combat ortho Euler X (90=top-down)</t>
+  </si>
+  <si>
+    <t>Defend+PushMap开战Combat正交相机Euler X（90=纯俯视；Prepare/Dig仍90）</t>
+  </si>
+  <si>
     <t>CameraOrthoSizeMargin</t>
   </si>
   <si>
@@ -748,6 +760,9 @@
     <t>Absolute leash = max(floor</t>
   </si>
   <si>
+    <t>r*mul)</t>
+  </si>
+  <si>
     <t>DeathKnockbackRatioCoeff</t>
   </si>
   <si>
@@ -842,6 +857,42 @@
   </si>
   <si>
     <t>尸体投射抛物线时长（秒；与t∈[0</t>
+  </si>
+  <si>
+    <t>DeathKnockbackShadowAlphaMul</t>
+  </si>
+  <si>
+    <t>击飞腾空地面黑影透明度</t>
+  </si>
+  <si>
+    <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+  </si>
+  <si>
+    <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+  </si>
+  <si>
+    <t>DeathKnockbackShadowScaleMin</t>
+  </si>
+  <si>
+    <t>击飞腾空地面黑影最小缩放</t>
+  </si>
+  <si>
+    <t>Min shadow diameter scale at ground height (0-1)</t>
+  </si>
+  <si>
+    <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+  </si>
+  <si>
+    <t>DeathKnockbackShadowBaseRadiusMul</t>
+  </si>
+  <si>
+    <t>击飞腾空地面黑影基准半径倍率</t>
+  </si>
+  <si>
+    <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+  </si>
+  <si>
+    <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
   </si>
   <si>
     <t>DeathDefendCorpseAlphaMul</t>
@@ -1868,15 +1919,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.8333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.5" style="2" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1912,20 +1957,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2039,7 +2084,7 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
@@ -2056,7 +2101,7 @@
         <v>44</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -2073,7 +2118,7 @@
         <v>48</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2090,7 +2135,7 @@
         <v>52</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -2107,7 +2152,7 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
@@ -2124,7 +2169,7 @@
         <v>60</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -2141,7 +2186,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.15</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -2158,7 +2203,7 @@
         <v>68</v>
       </c>
       <c r="C17">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D17" t="s">
         <v>69</v>
@@ -2175,7 +2220,7 @@
         <v>72</v>
       </c>
       <c r="C18">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D18" t="s">
         <v>73</v>
@@ -2209,7 +2254,7 @@
         <v>80</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -2226,7 +2271,7 @@
         <v>84</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
         <v>85</v>
@@ -2243,7 +2288,7 @@
         <v>88</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D22" t="s">
         <v>89</v>
@@ -2260,7 +2305,7 @@
         <v>92</v>
       </c>
       <c r="C23">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -2277,7 +2322,7 @@
         <v>96</v>
       </c>
       <c r="C24">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D24" t="s">
         <v>97</v>
@@ -2294,7 +2339,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D25" t="s">
         <v>101</v>
@@ -2311,7 +2356,7 @@
         <v>104</v>
       </c>
       <c r="C26">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="D26" t="s">
         <v>105</v>
@@ -2328,7 +2373,7 @@
         <v>108</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -2345,7 +2390,7 @@
         <v>112</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
         <v>113</v>
@@ -2362,7 +2407,7 @@
         <v>116</v>
       </c>
       <c r="C29">
-        <v>0.05</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
         <v>117</v>
@@ -2396,7 +2441,7 @@
         <v>124</v>
       </c>
       <c r="C31">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -2413,7 +2458,7 @@
         <v>128</v>
       </c>
       <c r="C32">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="s">
         <v>129</v>
@@ -2430,7 +2475,7 @@
         <v>132</v>
       </c>
       <c r="C33">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="D33" t="s">
         <v>133</v>
@@ -2447,7 +2492,7 @@
         <v>136</v>
       </c>
       <c r="C34">
-        <v>60</v>
+        <v>0.05</v>
       </c>
       <c r="D34" t="s">
         <v>137</v>
@@ -2464,7 +2509,7 @@
         <v>140</v>
       </c>
       <c r="C35">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
         <v>141</v>
@@ -2481,7 +2526,7 @@
         <v>144</v>
       </c>
       <c r="C36">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -2498,7 +2543,7 @@
         <v>148</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D37" t="s">
         <v>149</v>
@@ -2515,7 +2560,7 @@
         <v>152</v>
       </c>
       <c r="C38">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>153</v>
@@ -2532,7 +2577,7 @@
         <v>156</v>
       </c>
       <c r="C39">
-        <v>100</v>
+        <v>0.55</v>
       </c>
       <c r="D39" t="s">
         <v>157</v>
@@ -2549,7 +2594,7 @@
         <v>160</v>
       </c>
       <c r="C40">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
         <v>161</v>
@@ -2566,7 +2611,7 @@
         <v>164</v>
       </c>
       <c r="C41">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D41" t="s">
         <v>165</v>
@@ -2583,7 +2628,7 @@
         <v>168</v>
       </c>
       <c r="C42">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D42" t="s">
         <v>169</v>
@@ -2600,7 +2645,7 @@
         <v>172</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D43" t="s">
         <v>173</v>
@@ -2617,7 +2662,7 @@
         <v>176</v>
       </c>
       <c r="C44">
-        <v>0.1</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
         <v>177</v>
@@ -2634,7 +2679,7 @@
         <v>180</v>
       </c>
       <c r="C45">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D45" t="s">
         <v>181</v>
@@ -2651,7 +2696,7 @@
         <v>184</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="D46" t="s">
         <v>185</v>
@@ -2668,7 +2713,7 @@
         <v>188</v>
       </c>
       <c r="C47">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
         <v>189</v>
@@ -2685,7 +2730,7 @@
         <v>192</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>0.35</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
@@ -2702,7 +2747,7 @@
         <v>196</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
         <v>197</v>
@@ -2719,7 +2764,7 @@
         <v>200</v>
       </c>
       <c r="C50">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>201</v>
@@ -2736,7 +2781,7 @@
         <v>204</v>
       </c>
       <c r="C51">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="D51" t="s">
         <v>205</v>
@@ -2753,7 +2798,7 @@
         <v>208</v>
       </c>
       <c r="C52">
-        <v>50</v>
+        <v>0.85</v>
       </c>
       <c r="D52" t="s">
         <v>209</v>
@@ -2770,7 +2815,7 @@
         <v>212</v>
       </c>
       <c r="C53">
-        <v>0.35</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
         <v>213</v>
@@ -2787,7 +2832,7 @@
         <v>216</v>
       </c>
       <c r="C54">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="D54" t="s">
         <v>217</v>
@@ -2804,7 +2849,7 @@
         <v>220</v>
       </c>
       <c r="C55">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="D55" t="s">
         <v>221</v>
@@ -2821,7 +2866,7 @@
         <v>224</v>
       </c>
       <c r="C56">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="D56" t="s">
         <v>225</v>
@@ -2838,7 +2883,7 @@
         <v>228</v>
       </c>
       <c r="C57">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="D57" t="s">
         <v>229</v>
@@ -2855,7 +2900,7 @@
         <v>232</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -2872,238 +2917,304 @@
         <v>236</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D59" t="s">
         <v>237</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B60" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C61">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E62" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C63">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>254</v>
-      </c>
-      <c r="B64" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C64" s="1">
-        <v>6</v>
+      <c r="B64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64">
+        <v>0.2</v>
       </c>
       <c r="D64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C65">
-        <v>0.01</v>
+        <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C66">
-        <v>0.55</v>
+        <v>0.01</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>266</v>
-      </c>
-      <c r="B67" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C67" s="1">
-        <v>0.8</v>
+      <c r="B67" t="s">
+        <v>268</v>
+      </c>
+      <c r="C67">
+        <v>0.55</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C68">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C69">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C70">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E71" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C72">
+        <v>0.85</v>
+      </c>
+      <c r="D72" t="s">
+        <v>289</v>
+      </c>
+      <c r="E72" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>291</v>
+      </c>
+      <c r="B73" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73">
+        <v>0.4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>293</v>
+      </c>
+      <c r="E73" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74">
+        <v>0.7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>297</v>
+      </c>
+      <c r="E74" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>303</v>
+      </c>
+      <c r="B76" t="s">
+        <v>304</v>
+      </c>
+      <c r="C76">
         <v>12</v>
       </c>
-      <c r="D72" t="s">
-        <v>288</v>
-      </c>
-      <c r="E72" t="s">
-        <v>289</v>
+      <c r="D76" t="s">
+        <v>305</v>
+      </c>
+      <c r="E76" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="314">
   <si>
     <t>常量键</t>
   </si>
@@ -760,9 +760,6 @@
     <t>Absolute leash = max(floor</t>
   </si>
   <si>
-    <t>r*mul)</t>
-  </si>
-  <si>
     <t>DeathKnockbackRatioCoeff</t>
   </si>
   <si>
@@ -809,6 +806,30 @@
   </si>
   <si>
     <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
+  </si>
+  <si>
+    <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+  </si>
+  <si>
+    <t>死亡击飞方向半角扩散</t>
+  </si>
+  <si>
+    <t>Max yaw offset each side from base knockback direction (degrees)</t>
+  </si>
+  <si>
+    <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+  </si>
+  <si>
+    <t>DeathKnockbackDirectionRandomStepDegrees</t>
+  </si>
+  <si>
+    <t>死亡击飞方向随机步进</t>
+  </si>
+  <si>
+    <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+  </si>
+  <si>
+    <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
   </si>
   <si>
     <t>DeathKnockbackPeakHeight</t>
@@ -965,11 +986,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -977,7 +1005,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -985,14 +1013,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1000,7 +1028,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1008,7 +1036,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1016,7 +1044,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1024,7 +1052,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1032,14 +1060,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1047,7 +1075,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1055,7 +1083,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1063,14 +1091,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1078,42 +1106,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1426,162 +1454,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1634,7 +1655,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1644,7 +1665,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1654,44 +1675,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1718,15 +1739,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1753,7 +1773,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1765,163 +1784,173 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1957,20 +1986,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2940,281 +2969,317 @@
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
+        <v>242</v>
+      </c>
+      <c r="B61" t="s">
         <v>243</v>
-      </c>
-      <c r="B61" t="s">
-        <v>244</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
+        <v>244</v>
+      </c>
+      <c r="E61" t="s">
         <v>245</v>
-      </c>
-      <c r="E61" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
+        <v>246</v>
+      </c>
+      <c r="B62" t="s">
         <v>247</v>
-      </c>
-      <c r="B62" t="s">
-        <v>248</v>
       </c>
       <c r="C62">
         <v>0.5</v>
       </c>
       <c r="D62" t="s">
+        <v>248</v>
+      </c>
+      <c r="E62" t="s">
         <v>249</v>
-      </c>
-      <c r="E62" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" t="s">
         <v>251</v>
-      </c>
-      <c r="B63" t="s">
-        <v>252</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" t="s">
+        <v>252</v>
+      </c>
+      <c r="E63" t="s">
         <v>253</v>
-      </c>
-      <c r="E63" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
+        <v>254</v>
+      </c>
+      <c r="B64" t="s">
         <v>255</v>
-      </c>
-      <c r="B64" t="s">
-        <v>256</v>
       </c>
       <c r="C64">
         <v>0.2</v>
       </c>
       <c r="D64" t="s">
+        <v>256</v>
+      </c>
+      <c r="E64" t="s">
         <v>257</v>
-      </c>
-      <c r="E64" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
+        <v>258</v>
+      </c>
+      <c r="B65" t="s">
         <v>259</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65">
+        <v>30</v>
+      </c>
+      <c r="D65" t="s">
         <v>260</v>
       </c>
-      <c r="C65">
-        <v>6</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>261</v>
-      </c>
-      <c r="E65" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
+        <v>262</v>
+      </c>
+      <c r="B66" t="s">
         <v>263</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
         <v>264</v>
       </c>
-      <c r="C66">
-        <v>0.01</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>265</v>
-      </c>
-      <c r="E66" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
+        <v>266</v>
+      </c>
+      <c r="B67" t="s">
         <v>267</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
         <v>268</v>
       </c>
-      <c r="C67">
-        <v>0.55</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>269</v>
-      </c>
-      <c r="E67" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
+        <v>270</v>
+      </c>
+      <c r="B68" t="s">
         <v>271</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68">
+        <v>0.01</v>
+      </c>
+      <c r="D68" t="s">
         <v>272</v>
       </c>
-      <c r="C68">
-        <v>0.8</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>273</v>
-      </c>
-      <c r="E68" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
+        <v>274</v>
+      </c>
+      <c r="B69" t="s">
         <v>275</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69">
+        <v>0.55</v>
+      </c>
+      <c r="D69" t="s">
         <v>276</v>
       </c>
-      <c r="C69">
-        <v>0.6</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>277</v>
-      </c>
-      <c r="E69" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
+        <v>278</v>
+      </c>
+      <c r="B70" t="s">
         <v>279</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70">
+        <v>0.8</v>
+      </c>
+      <c r="D70" t="s">
         <v>280</v>
       </c>
-      <c r="C70">
-        <v>0.35</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>281</v>
-      </c>
-      <c r="E70" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
+        <v>282</v>
+      </c>
+      <c r="B71" t="s">
         <v>283</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71">
+        <v>0.6</v>
+      </c>
+      <c r="D71" t="s">
         <v>284</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>285</v>
-      </c>
-      <c r="E71" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
+        <v>286</v>
+      </c>
+      <c r="B72" t="s">
         <v>287</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72">
+        <v>0.35</v>
+      </c>
+      <c r="D72" t="s">
         <v>288</v>
       </c>
-      <c r="C72">
-        <v>0.85</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>289</v>
-      </c>
-      <c r="E72" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
+        <v>290</v>
+      </c>
+      <c r="B73" t="s">
         <v>291</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
         <v>292</v>
       </c>
-      <c r="C73">
-        <v>0.4</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>293</v>
-      </c>
-      <c r="E73" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
+        <v>294</v>
+      </c>
+      <c r="B74" t="s">
         <v>295</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74">
+        <v>0.85</v>
+      </c>
+      <c r="D74" t="s">
         <v>296</v>
       </c>
-      <c r="C74">
-        <v>0.7</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>297</v>
-      </c>
-      <c r="E74" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" t="s">
         <v>299</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75">
+        <v>0.4</v>
+      </c>
+      <c r="D75" t="s">
         <v>300</v>
       </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>301</v>
-      </c>
-      <c r="E75" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
+        <v>302</v>
+      </c>
+      <c r="B76" t="s">
         <v>303</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76">
+        <v>0.7</v>
+      </c>
+      <c r="D76" t="s">
         <v>304</v>
       </c>
-      <c r="C76">
+      <c r="E76" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>306</v>
+      </c>
+      <c r="B77" t="s">
+        <v>307</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>308</v>
+      </c>
+      <c r="E77" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>310</v>
+      </c>
+      <c r="B78" t="s">
+        <v>311</v>
+      </c>
+      <c r="C78">
         <v>12</v>
       </c>
-      <c r="D76" t="s">
-        <v>305</v>
-      </c>
-      <c r="E76" t="s">
-        <v>306</v>
+      <c r="D78" t="s">
+        <v>312</v>
+      </c>
+      <c r="E78" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -986,14 +986,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1455,148 +1448,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1951,6 +1944,10 @@
   <sheetPr/>
   <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -623,9 +623,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1038,11 +1044,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" min="1" max="1"/>
-    <col width="13.25" customWidth="1" min="2" max="2"/>
+    <col width="31.625" customWidth="1" min="2" max="2"/>
+    <col width="14.75" customWidth="1" style="2" min="3" max="3"/>
+    <col width="15.875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1064,7 @@
           <t>主键中文翻译</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
@@ -1083,7 +1091,7 @@
           <t>展示用中文名；运行时不读</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1110,7 +1118,7 @@
           <t>ConstantKeyZh</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1137,7 +1145,7 @@
           <t>普攻主属性倍率</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -1162,7 +1170,7 @@
           <t>攻击速度基础值</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1187,7 +1195,7 @@
           <t>攻击速度敏捷除数</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>60</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1212,7 +1220,7 @@
           <t>技能冷却智力除数</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1237,7 +1245,7 @@
           <t>技能冷却下限</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1262,7 +1270,7 @@
           <t>血量力量系数</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1287,7 +1295,7 @@
           <t>镜头高度</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1312,7 +1320,7 @@
           <t>战斗相机倾角</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>85</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1337,7 +1345,7 @@
           <t>地图适配Size余量</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1362,7 +1370,7 @@
           <t>推图开战默认Size</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1387,7 +1395,7 @@
           <t>推图布阵默认Size</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1412,7 +1420,7 @@
           <t>镜头近裁剪面</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1437,7 +1445,7 @@
           <t>镜头远裁剪面</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>100</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1462,7 +1470,7 @@
           <t>跟随死区半径</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1487,7 +1495,7 @@
           <t>跟随平滑时间</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1512,7 +1520,7 @@
           <t>滚轮缩放步进</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1537,7 +1545,7 @@
           <t>正交Size下限</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1562,7 +1570,7 @@
           <t>正交Size上限</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1587,7 +1595,7 @@
           <t>拖拽启动像素阈值</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1612,7 +1620,7 @@
           <t>推图镜头预览速度</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>12</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1637,7 +1645,7 @@
           <t>推图镜头预览路点停留</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1654,1400 +1662,2245 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DigTriggerDwellSeconds</t>
+          <t>SearchExtractHoldOrthoSizeMin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>挖坟触发停留</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.2</v>
+          <t>搜打撤守点Size下限</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cursor dwell before DigAction starts</t>
+          <t>HoldFraming ortho Size floor (intersect CameraOrthoSizeMin)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+          <t>HoldFraming 正交 Size 下限（再与 CameraOrthoSizeMin 取交）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BaseDigDuration</t>
+          <t>SearchExtractHoldOrthoSizeMax</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>挖坟基础时长</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.8</v>
+          <t>搜打撤守点Size上限</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BaseDigDuration seconds</t>
+          <t>HoldFraming ortho Size ceiling (intersect CameraOrthoSizeMax)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DigActionDuration=max(下限</t>
+          <t>HoldFraming 正交 Size 上限（再与 CameraOrthoSizeMax 取交）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DigActionDurationFloor</t>
+          <t>SearchExtractHoldMaxPanRadius</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>挖坟最短时长</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.1</v>
+          <t>守点中心偏移半径</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Min DigActionDuration seconds</t>
+          <t>Max look-at distance from current Objective world XZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>单次挖坟最短秒数（公式地板）</t>
+          <t>look-at 距当前 Objective 世界 XZ 最大半径；圈外忠诚兵允许出镜</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AttackSlotMeleeCount</t>
+          <t>SearchExtractHoldViewportPad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>近战攻击位数量</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>12</v>
+          <t>守点视口边垫</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0.08</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Melee AttackSlot ring slot count</t>
+          <t>Outer viewport pad on four sides (0-0.5)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>近战单位围绕目标可占用的攻击位数量</t>
+          <t>外框四边视口垫（0～0.5）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AttackSlotRangedCount</t>
+          <t>SearchExtractHoldTopHudPad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>远程攻击位数量</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>8</v>
+          <t>守点顶HUD垫</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0.12</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ranged AttackSlot ring slot count</t>
+          <t>Extra top pad for CountdownBar / CombatIndicator</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>远程单位围绕目标可占用的攻击位数量</t>
+          <t>外框顶边额外垫（CountdownBar / CombatIndicator）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AttackSlotMargin</t>
+          <t>SearchExtractHoldInnerPad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>攻击位环半径余量</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.05</v>
+          <t>守点内框垫</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0.18</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ring radius = reach sum - margin</t>
+          <t>Inner pad; tighten only after all stay inside for dwell</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>攻击位环半径计算时从可达距离减去的余量</t>
+          <t>内框边垫；全体在内框内满滞留才允许收紧</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AttackSlotMinRingRadius</t>
+          <t>SearchExtractHoldZoomInDelaySeconds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>攻击位环最小半径</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.05</v>
+          <t>守点拉近滞留秒</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min AttackSlot ring radius</t>
+          <t>Dwell seconds before allowing Size shrink / recenter</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>攻击位环半径下限</t>
+          <t>内框滞留后才允许减小 Size / 回中</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AttackSlotReclaimMoveThreshold</t>
+          <t>SearchExtractHoldSmoothTimeOut</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>攻击位重算位移阈值</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.5</v>
+          <t>守点拉远平滑秒</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Target move distance to recompute slots</t>
+          <t>SmoothDamp when expanding Size / pan-out</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>目标移动超过本距离时重算攻击位</t>
+          <t>Size/中心拉远（扩大）SmoothDamp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AttackSlotDefaultTargetBodyRadius</t>
+          <t>SearchExtractHoldSmoothTimeIn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>默认目标体半径</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.35</v>
+          <t>守点拉近平滑秒</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fallback target BodyRadius</t>
+          <t>SmoothDamp when tightening; must be &gt; Out</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>缺体外观/怪物半径时的默认目标体半径</t>
+          <t>Size/中心拉近（收紧）SmoothDamp；须大于 Out</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HitConfirmSlack</t>
+          <t>SearchExtractHoldSampleInterval</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>命中确认松弛距离</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.05</v>
+          <t>守点采样间隔秒</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HitConfirm range slack</t>
+          <t>Low-frequency viewport AABB sample interval seconds</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+          <t>视口 AABB 低频采样间隔</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SurroundGapDegrees</t>
+          <t>SearchExtractHoldObjectiveBias</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>包围缺口角度</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>60</v>
+          <t>守点中心偏向</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Surround gap sector degrees</t>
+          <t>look-at = lerp(soldier center, Objective, bias); 1=pin Objective</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+          <t>look-at = lerp(士兵中心, Objective, bias)；1=钉 Objective</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>StuckDetectWindowSeconds</t>
+          <t>DigTriggerDwellSeconds</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>卡死检测窗口</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.5</v>
+          <t>挖坟触发停留</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>StuckHold detect window seconds</t>
+          <t>Cursor dwell before DigAction starts</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>有移动意图但位移不足时的检测窗口秒数</t>
+          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>StuckDisplacementEpsilon</t>
+          <t>BaseDigDuration</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>卡死位移阈值</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.2</v>
+          <t>挖坟基础时长</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>StuckHold displacement epsilon</t>
+          <t>BaseDigDuration seconds</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>检测窗口内XZ位移小于本值则判定卡住</t>
+          <t>DigActionDuration=max(下限</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>StuckHoldSeconds</t>
+          <t>DigActionDurationFloor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>卡死停顿时长</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
+          <t>挖坟最短时长</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>StuckHold force-Idle seconds</t>
+          <t>Min DigActionDuration seconds</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>判定卡住后强制Idle的秒数</t>
+          <t>单次挖坟最短秒数（公式地板）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ProjectileDefaultHitRadius</t>
+          <t>AttackSlotMeleeCount</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>投射物默认命中半径</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.55</v>
+          <t>近战攻击位数量</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Default projectile soft-hit radius</t>
+          <t>Melee AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+          <t>近战单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DefendVictoryStageExp</t>
+          <t>AttackSlotRangedCount</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>防守胜利阶段经验</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>100</v>
+          <t>远程攻击位数量</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Defend victory Demo stage Exp</t>
+          <t>Ranged AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defend清场胜利结算时入账的阶段经验</t>
+          <t>远程单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FlowFieldDefaultCellSize</t>
+          <t>AttackSlotMargin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>流场默认格宽</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.5</v>
+          <t>攻击位环半径余量</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FlowField default cell size</t>
+          <t>Ring radius = reach sum - margin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>共享目标流场默认格子边长</t>
+          <t>攻击位环半径计算时从可达距离减去的余量</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FlowFieldMinCellSize</t>
+          <t>AttackSlotMinRingRadius</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>流场最小格宽</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.25</v>
+          <t>攻击位环最小半径</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FlowField min cell size</t>
+          <t>Min AttackSlot ring radius</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>流场格宽下限（性能降级时可抬高）</t>
+          <t>攻击位环半径下限</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FlowFieldMaxCellSize</t>
+          <t>AttackSlotReclaimMoveThreshold</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>流场最大格宽</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+          <t>攻击位重算位移阈值</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FlowField max cell size</t>
+          <t>Target move distance to recompute slots</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>流场格宽上限</t>
+          <t>目标移动超过本距离时重算攻击位</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MassMoveMaxRecalcPerFrame</t>
+          <t>AttackSlotDefaultTargetBodyRadius</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>群体移动每帧重算上限</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>50</v>
+          <t>默认目标体半径</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MassMove/AttackSlot refresh budget per frame</t>
+          <t>Fallback target BodyRadius</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>每帧最多重算路径/攻击位的单位数</t>
+          <t>缺体外观/怪物半径时的默认目标体半径</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MassMoveDefaultAgentRadius</t>
+          <t>HitConfirmSlack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>群体移动默认体半径</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.1</v>
+          <t>命中确认松弛距离</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Default mass-move agent radius</t>
+          <t>HitConfirm range slack</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>群体移动登记时的默认体半径</t>
+          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MassMoveArriveEpsilon</t>
+          <t>SurroundGapDegrees</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>群体移动到达阈值</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.08</v>
+          <t>包围缺口角度</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Arrive epsilon for DesiredDestination</t>
+          <t>Surround gap sector degrees</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>到达期望点判定的距离阈值</t>
+          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MassMoveDefaultObjectiveArriveRadius</t>
+          <t>StuckDetectWindowSeconds</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>目标到达默认半径</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
+          <t>卡死检测窗口</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Default Objective arrive radius</t>
+          <t>StuckHold detect window seconds</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+          <t>有移动意图但位移不足时的检测窗口秒数</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MassMoveAttackSlotSeparationScale</t>
+          <t>StuckDisplacementEpsilon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>攻击位软分离系数</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.35</v>
+          <t>卡死位移阈值</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LocalDetour separation scale in AttackSlot</t>
+          <t>StuckHold displacement epsilon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+          <t>检测窗口内XZ位移小于本值则判定卡住</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SoftCollisionMaxCorrectionSpeed</t>
+          <t>StuckHoldSeconds</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>软碰撞最大修正速度</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2</v>
+          <t>卡死停顿时长</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Soft collision max correction speed</t>
+          <t>StuckHold force-Idle seconds</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>软碰撞位置修正速度上限（单位/秒）</t>
+          <t>判定卡住后强制Idle的秒数</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LocalDetourProbeLength</t>
+          <t>ProjectileDefaultHitRadius</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>本地绕行探测长度</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
+          <t>投射物默认命中半径</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LocalDetour L/R probe length</t>
+          <t>Default projectile soft-hit radius</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>左右绕行探测射线长度</t>
+          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LocalDetourSoftSeparationStrength</t>
+          <t>DefendVictoryStageExp</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>本地绕行软分离强度</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.15</v>
+          <t>防守胜利阶段经验</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LocalDetour soft separation strength</t>
+          <t>Defend victory Demo stage Exp</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>友军软分离推力强度</t>
+          <t>Defend清场胜利结算时入账的阶段经验</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LocalDetourDetourBias</t>
+          <t>FlowFieldDefaultCellSize</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>本地绕行偏置</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.85</v>
+          <t>流场默认格宽</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LocalDetour L/R bias blend</t>
+          <t>FlowField default cell size</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>绕行方向与原期望方向的混合偏置</t>
+          <t>共享目标流场默认格子边长</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LocalDetourForwardConeHalfAngleDeg</t>
+          <t>FlowFieldMinCellSize</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>本地绕行前向锥半角</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>50</v>
+          <t>流场最小格宽</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Forward block cone half-angle degrees</t>
+          <t>FlowField min cell size</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>判定前方友军阻挡的圆锥半角（度）</t>
+          <t>流场格宽下限（性能降级时可抬高）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BossAdvanceArriveRadius</t>
+          <t>FlowFieldMaxCellSize</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Boss推进到达半径</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.35</v>
+          <t>流场最大格宽</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BossPoint advance arrive radius</t>
+          <t>FlowField max cell size</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>目标链耗尽后推进Boss点的到达半径</t>
+          <t>流场格宽上限</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EngageStickHysteresisMargin</t>
+          <t>MassMoveMaxRecalcPerFrame</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>接战粘滞余量</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.15</v>
+          <t>群体移动每帧重算上限</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Engage sticky retarget hysteresis</t>
+          <t>MassMove/AttackSlot refresh budget per frame</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+          <t>每帧最多重算路径/攻击位的单位数</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetSeconds</t>
+          <t>MassMoveDefaultAgentRadius</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>追击卡住换目标秒数</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
+          <t>群体移动默认体半径</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chase out-of-range stuck force-retarget window seconds</t>
+          <t>Default mass-move agent radius</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
+          <t>群体移动登记时的默认体半径</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetCooldownSeconds</t>
+          <t>MassMoveArriveEpsilon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>追击卡住换目标冷却</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
+          <t>群体移动到达阈值</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0.08</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cooldown after chase-stuck force retarget</t>
+          <t>Arrive epsilon for DesiredDestination</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>强制换目标后冷却，防A↔B来回甩</t>
+          <t>到达期望点判定的距离阈值</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PushMapSpawnMinSampleDistance</t>
+          <t>MassMoveDefaultObjectiveArriveRadius</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>刷怪散布最小采样距</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.75</v>
+          <t>目标到达默认半径</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PushMap spawn min sample distance</t>
+          <t>Default Objective arrive radius</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>刷怪散布环形采样的最小间距</t>
+          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PushMapSpawnSampleDistanceBodyMul</t>
+          <t>MassMoveAttackSlotSeparationScale</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>刷怪散布体半径倍数</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>2.5</v>
+          <t>攻击位软分离系数</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Spawn sample distance = max(min</t>
+          <t>LocalDetour separation scale in AttackSlot</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PushMapSpawnLeashSlack</t>
+          <t>SoftCollisionMaxCorrectionSpeed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>刷怪拴绳松弛</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.35</v>
+          <t>软碰撞最大修正速度</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NavMesh sample leash slack</t>
+          <t>Soft collision max correction speed</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+          <t>软碰撞位置修正速度上限（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashFloor</t>
+          <t>LocalDetourProbeLength</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳下限</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>3</v>
+          <t>本地绕行探测长度</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Absolute leash floor</t>
+          <t>LocalDetour L/R probe length</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳距离下限</t>
+          <t>左右绕行探测射线长度</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+          <t>LocalDetourSoftSeparationStrength</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳体倍数</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>10</v>
+          <t>本地绕行软分离强度</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.15</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Absolute leash = max(floor</t>
+          <t>LocalDetour soft separation strength</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>友军软分离推力强度</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DeathKnockbackRatioCoeff</t>
+          <t>LocalDetourDetourBias</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>死亡击飞比例系数</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3</v>
+          <t>本地绕行偏置</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0.85</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
+          <t>LocalDetour L/R bias blend</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
+          <t>绕行方向与原期望方向的混合偏置</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DeathKnockbackMinDistance</t>
+          <t>LocalDetourForwardConeHalfAngleDeg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>死亡击飞最小距离</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.5</v>
+          <t>本地绕行前向锥半角</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Death knockback distance floor</t>
+          <t>Forward block cone half-angle degrees</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离下限（世界单位）</t>
+          <t>判定前方友军阻挡的圆锥半角（度）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DeathKnockbackMaxDistance</t>
+          <t>BossAdvanceArriveRadius</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>死亡击飞最大距离</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>2</v>
+          <t>Boss推进到达半径</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Death knockback distance ceiling</t>
+          <t>BossPoint advance arrive radius</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+          <t>目标链耗尽后推进Boss点的到达半径</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DeathDie2KnockbackThreshold</t>
+          <t>EngageStickHysteresisMargin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>死亡Die2击退阈值</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.2</v>
+          <t>接战粘滞余量</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0.15</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
+          <t>Engage sticky retarget hysteresis</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
+          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+          <t>ChaseStuckRetargetSeconds</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>死亡击飞方向半角扩散</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>30</v>
+          <t>追击卡住换目标秒数</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Max yaw offset each side from base knockback direction (degrees)</t>
+          <t>Chase out-of-range stuck force-retarget window seconds</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionRandomStepDegrees</t>
+          <t>ChaseStuckRetargetCooldownSeconds</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>死亡击飞方向随机步进</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>5</v>
+          <t>追击卡住换目标冷却</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+          <t>Cooldown after chase-stuck force retarget</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
+          <t>强制换目标后冷却，防A↔B来回甩</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DeathKnockbackPeakHeight</t>
+          <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>死亡击飞抛物线峰值高度</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>6</v>
+          <t>刷怪散布最小采样距</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Corpse projectile Y arc peak (world units)</t>
+          <t>PushMap spawn min sample distance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+          <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashDamageMul</t>
+          <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>尸体砸击伤害系数</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.01</v>
+          <t>刷怪散布体半径倍数</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2.5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+          <t>Spawn sample distance = max(min</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashHitRadius</t>
+          <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>尸体砸击命中半径</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>0.55</v>
+          <t>刷怪拴绳松弛</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>In-flight/landing soft-hit radius</t>
+          <t>NavMesh sample leash slack</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DeathKnockbackSeconds</t>
+          <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>死亡击飞时长</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>0.8</v>
+          <t>刷怪绝对拴绳下限</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Corpse projectile parabolic duration (seconds)</t>
+          <t>Absolute leash floor</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>尸体投射抛物线时长（秒；与t∈[0</t>
+          <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowAlphaMul</t>
+          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影透明度</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0.6</v>
+          <t>刷怪绝对拴绳体倍数</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+          <t>Absolute leash = max(floor</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowScaleMin</t>
+          <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影最小缩放</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0.35</v>
+          <t>死亡击飞比例系数</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Min shadow diameter scale at ground height (0-1)</t>
+          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowBaseRadiusMul</t>
+          <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影基准半径倍率</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
+          <t>死亡击飞最小距离</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+          <t>Death knockback distance floor</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DeathDefendCorpseAlphaMul</t>
+          <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Defend尸体透明度系数</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0.85</v>
+          <t>死亡击飞最大距离</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Defend corpse sprite alpha multiplier</t>
+          <t>Death knockback distance ceiling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Defend怪/士兵尸体透明度×本值</t>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DeathCorpseDarkenMul</t>
+          <t>DeathDie2KnockbackThreshold</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>尸体变暗系数</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0.4</v>
+          <t>死亡Die2击退阈值</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Permanent-death corpse RGB multiplier</t>
+          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DeathFakeDeathCorpseDarkenMul</t>
+          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>假死尸体变暗系数</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0.7</v>
+          <t>死亡击飞方向半角扩散</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PushMap fake-death corpse RGB multiplier</t>
+          <t>Max yaw offset each side from base knockback direction (degrees)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PushMap假死尸体RGB×本值</t>
+          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScalePerHit</t>
+          <t>DeathKnockbackDirectionRandomStepDegrees</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>士兵命中体型步进</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2</v>
+          <t>死亡击飞方向随机步进</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>DeathKnockbackPeakHeight</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>死亡击飞抛物线峰值高度</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Corpse projectile Y arc peak (world units)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashDamageMul</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害系数</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DeathCorpseSmashHitRadius</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>尸体砸击命中半径</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>In-flight/landing soft-hit radius</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DeathKnockbackSeconds</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>死亡击飞时长</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Corpse projectile parabolic duration (seconds)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>尸体投射抛物线时长（秒；与t∈[0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowAlphaMul</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影透明度</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowScaleMin</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影最小缩放</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Min shadow diameter scale at ground height (0-1)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DeathKnockbackShadowBaseRadiusMul</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>击飞腾空地面黑影基准半径倍率</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DeathDefendCorpseAlphaMul</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Defend尸体透明度系数</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Defend corpse sprite alpha multiplier</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Defend怪/士兵尸体透明度×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Permanent-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>假死尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PushMap fake-death corpse RGB multiplier</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PushMap假死尸体RGB×本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WarriorVisualModelScalePerHit</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>士兵命中体型步进</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>WarriorVisualModelScaleMax</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>士兵模型缩放上限</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C91" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>VisualModelScale每次命中apply末尾夹紧上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyDropIntervalSeconds</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>自动制造尸骸落下间隔</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Seconds between body-rain drop batches</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>UI-016 StepA：每批次掉落间隔秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AutoMfgDropCountMin</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>自动制造尸骸每批最少</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Min pieces per drop batch</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>StepA 每间隔随机落下件数下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AutoMfgDropCountMax</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>自动制造尸骸每批最多</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Max pieces per drop batch</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>StepA 每间隔随机落下件数上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AutoMfgGravityScale</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>自动制造尸骸重力</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Rigidbody2D gravityScale for body pieces</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Rigidbody2D.gravityScale</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AutoMfgBounciness</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>自动制造尸骸弹性</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PhysicsMaterial2D bounciness</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PhysicsMaterial2D.bounciness</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AutoMfgFriction</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>自动制造尸骸摩擦</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PhysicsMaterial2D friction</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PhysicsMaterial2D.friction</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AutoMfgColliderInset</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>自动制造尸骸碰撞内缩</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AutoMfgSpawnAngleMaxDeg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>自动制造尸骸落下转角</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>50</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AutoMfgSpawnJitterXPx</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>自动制造尸骸水平微扰</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Random spawn X jitter in ref pixels</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>落点相对屏幕中心 X 微扰</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AutoMfgMagicCircleFlashHz</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>自动制造法阵闪红频率</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Magic circle red flash Hz during StepB</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>StepB 法阵红色闪烁 Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AutoMfgReviveSpawnOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>自动制造复活出生上偏移</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Revive spawn Y offset from pile base px</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>问号/士兵出生相对堆底向上像素</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AutoMfgPileFloorYPx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>自动制造尸骸堆地板 Y</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>-300</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Body pile floor Y in ref pixels</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2D 演出层堆地板相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierLandYPx</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>自动制造士兵落地 Y</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>-410</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Revived soldier idle land Y px</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>复活士兵落地相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>自动制造躯体适配边长</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>49</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>StepA body Image max edge px (~35% of prior 140)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>自动制造士兵固定边长</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>64</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowWidthPx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子宽</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>20</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow width ref px</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子宽（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowHeightPx</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子高</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow height ref px</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子高（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowAlpha</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子透明度</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Foot-shadow black Alpha 0-1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>脚下影子黑色 Alpha（0～1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AutoMfgUseLegacySoldierRow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>自动制造旧士兵行开关</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1=legacy SoldierScroll conveyor</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierVisualScale</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>自动制造士兵视觉缩放</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Revive piece localScale XYZ</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>复活件 localScale（XYZ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-40</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier center</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>影子相对士兵中心的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAngleMaxDeg</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>自动制造躯体绝对转角上限</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>270</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Clamp body Z angle abs deg; zero omega at limit</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" min="1" max="1"/>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1937,1968 +1937,2214 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DigTriggerDwellSeconds</t>
+          <t>SearchExtractDecisionIdleDelaySeconds</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>挖坟触发停留</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0.2</v>
+          <t>决策停步延迟秒</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cursor dwell before DigAction starts</t>
+          <t>UI-032 show then delay before loyal MassMove pause + Idle</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
+          <t>UI-032 弹出后忠诚兵延迟停步并 Idle（任意搜集点数）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BaseDigDuration</t>
+          <t>SearchExtractDecisionAutoLeaveSeconds</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>挖坟基础时长</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0.8</v>
+          <t>单点自动离开秒</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BaseDigDuration seconds</t>
+          <t>Only GatherPointCount=1: LeaveButton countdown then auto-Leave</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DigActionDuration=max(下限</t>
+          <t>仅 GatherPointCount=1 时 LeaveButton 倒计时后自动 Leave</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DigActionDurationFloor</t>
+          <t>OffScreenSpawnHintIntroBlinkSeconds</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>挖坟最短时长</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0.1</v>
+          <t>离屏来袭开场闪红秒</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Min DigActionDuration seconds</t>
+          <t>UI-034: intro red-blink window seconds</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>单次挖坟最短秒数（公式地板）</t>
+          <t>UI-034：开场闪红总时长秒</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AttackSlotMeleeCount</t>
+          <t>OffScreenSpawnHintIntroBlinkCount</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>近战攻击位数量</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>12</v>
+          <t>离屏来袭开场闪红次数</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Melee AttackSlot ring slot count</t>
+          <t>UI-034: red blink count inside intro window</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>近战单位围绕目标可占用的攻击位数量</t>
+          <t>UI-034：开场窗口内闪红次数</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AttackSlotRangedCount</t>
+          <t>OffScreenSpawnHintHoldSeconds</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>远程攻击位数量</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>8</v>
+          <t>离屏来袭常亮秒</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ranged AttackSlot ring slot count</t>
+          <t>UI-034: solid white hold seconds after intro blink</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>远程单位围绕目标可占用的攻击位数量</t>
+          <t>UI-034：闪红后常亮秒数</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AttackSlotMargin</t>
+          <t>OffScreenSpawnHintDisplayScale</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>攻击位环半径余量</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0.05</v>
+          <t>离屏来袭显示缩放</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ring radius = reach sum - margin</t>
+          <t>UI-034: icon localScale while visible</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>攻击位环半径计算时从可达距离减去的余量</t>
+          <t>UI-034：显示期间图标 localScale</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AttackSlotMinRingRadius</t>
+          <t>OffScreenSpawnHintEdgeMarginPx</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>攻击位环最小半径</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0.05</v>
+          <t>离屏来袭边距像素</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>48</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Min AttackSlot ring radius</t>
+          <t>UI-034: icon center margin from screen edge (ref 1920x1080 px)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>攻击位环半径下限</t>
+          <t>UI-034：图标中心距参考分辨率屏幕边的像素边距</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AttackSlotReclaimMoveThreshold</t>
+          <t>OffScreenSpawnHintIconSizePx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>攻击位重算位移阈值</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0.5</v>
+          <t>离屏来袭图标边长</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>72</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Target move distance to recompute slots</t>
+          <t>UI-034: EnemyAttack_1 sizeDelta edge (ref 1920x1080)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>目标移动超过本距离时重算攻击位</t>
+          <t>UI-034：EnemyAttack_1 sizeDelta 边长（参考 1920×1080）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AttackSlotDefaultTargetBodyRadius</t>
+          <t>DigTriggerDwellSeconds</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>默认目标体半径</t>
+          <t>挖坟触发停留</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fallback target BodyRadius</t>
+          <t>Cursor dwell before DigAction starts</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>缺体外观/怪物半径时的默认目标体半径</t>
+          <t>光标与可挖坟相交并停留达到本秒数后触发DigAction</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HitConfirmSlack</t>
+          <t>BaseDigDuration</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>命中确认松弛距离</t>
+          <t>挖坟基础时长</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HitConfirm range slack</t>
+          <t>BaseDigDuration seconds</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
+          <t>DigActionDuration=max(下限</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SurroundGapDegrees</t>
+          <t>DigActionDurationFloor</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>包围缺口角度</t>
+          <t>挖坟最短时长</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>60</v>
+        <v>0.1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Surround gap sector degrees</t>
+          <t>Min DigActionDuration seconds</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
+          <t>单次挖坟最短秒数（公式地板）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>StuckDetectWindowSeconds</t>
+          <t>AttackSlotMeleeCount</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>卡死检测窗口</t>
+          <t>近战攻击位数量</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>StuckHold detect window seconds</t>
+          <t>Melee AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>有移动意图但位移不足时的检测窗口秒数</t>
+          <t>近战单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>StuckDisplacementEpsilon</t>
+          <t>AttackSlotRangedCount</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>卡死位移阈值</t>
+          <t>远程攻击位数量</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>StuckHold displacement epsilon</t>
+          <t>Ranged AttackSlot ring slot count</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>检测窗口内XZ位移小于本值则判定卡住</t>
+          <t>远程单位围绕目标可占用的攻击位数量</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>StuckHoldSeconds</t>
+          <t>AttackSlotMargin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>卡死停顿时长</t>
+          <t>攻击位环半径余量</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>StuckHold force-Idle seconds</t>
+          <t>Ring radius = reach sum - margin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>判定卡住后强制Idle的秒数</t>
+          <t>攻击位环半径计算时从可达距离减去的余量</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ProjectileDefaultHitRadius</t>
+          <t>AttackSlotMinRingRadius</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>投射物默认命中半径</t>
+          <t>攻击位环最小半径</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.55</v>
+        <v>0.05</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Default projectile soft-hit radius</t>
+          <t>Min AttackSlot ring radius</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
+          <t>攻击位环半径下限</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DefendVictoryStageExp</t>
+          <t>AttackSlotReclaimMoveThreshold</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>防守胜利阶段经验</t>
+          <t>攻击位重算位移阈值</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Defend victory Demo stage Exp</t>
+          <t>Target move distance to recompute slots</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Defend清场胜利结算时入账的阶段经验</t>
+          <t>目标移动超过本距离时重算攻击位</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FlowFieldDefaultCellSize</t>
+          <t>AttackSlotDefaultTargetBodyRadius</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>流场默认格宽</t>
+          <t>默认目标体半径</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FlowField default cell size</t>
+          <t>Fallback target BodyRadius</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>共享目标流场默认格子边长</t>
+          <t>缺体外观/怪物半径时的默认目标体半径</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FlowFieldMinCellSize</t>
+          <t>HitConfirmSlack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>流场最小格宽</t>
+          <t>命中确认松弛距离</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FlowField min cell size</t>
+          <t>HitConfirm range slack</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>流场格宽下限（性能降级时可抬高）</t>
+          <t>前摇结束命中确认时在攻击距离上额外允许的松弛</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FlowFieldMaxCellSize</t>
+          <t>SurroundGapDegrees</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>流场最大格宽</t>
+          <t>包围缺口角度</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FlowField max cell size</t>
+          <t>Surround gap sector degrees</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>流场格宽上限</t>
+          <t>近战多打一时攻击位环上预留的缺口扇区角度</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MassMoveMaxRecalcPerFrame</t>
+          <t>StuckDetectWindowSeconds</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>群体移动每帧重算上限</t>
+          <t>卡死检测窗口</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MassMove/AttackSlot refresh budget per frame</t>
+          <t>StuckHold detect window seconds</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>每帧最多重算路径/攻击位的单位数</t>
+          <t>有移动意图但位移不足时的检测窗口秒数</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MassMoveDefaultAgentRadius</t>
+          <t>StuckDisplacementEpsilon</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>群体移动默认体半径</t>
+          <t>卡死位移阈值</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Default mass-move agent radius</t>
+          <t>StuckHold displacement epsilon</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>群体移动登记时的默认体半径</t>
+          <t>检测窗口内XZ位移小于本值则判定卡住</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MassMoveArriveEpsilon</t>
+          <t>StuckHoldSeconds</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>群体移动到达阈值</t>
+          <t>卡死停顿时长</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Arrive epsilon for DesiredDestination</t>
+          <t>StuckHold force-Idle seconds</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>到达期望点判定的距离阈值</t>
+          <t>判定卡住后强制Idle的秒数</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MassMoveDefaultObjectiveArriveRadius</t>
+          <t>ProjectileDefaultHitRadius</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>目标到达默认半径</t>
+          <t>投射物默认命中半径</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Default Objective arrive radius</t>
+          <t>Default projectile soft-hit radius</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
+          <t>远程投射物默认软命中半径（表缺列时兜底）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MassMoveAttackSlotSeparationScale</t>
+          <t>DefendVictoryStageExp</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>攻击位软分离系数</t>
+          <t>防守胜利阶段经验</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0.35</v>
+        <v>100</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LocalDetour separation scale in AttackSlot</t>
+          <t>Defend victory Demo stage Exp</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
+          <t>Defend清场胜利结算时入账的阶段经验</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SoftCollisionMaxCorrectionSpeed</t>
+          <t>FlowFieldDefaultCellSize</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>软碰撞最大修正速度</t>
+          <t>流场默认格宽</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Soft collision max correction speed</t>
+          <t>FlowField default cell size</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>软碰撞位置修正速度上限（单位/秒）</t>
+          <t>共享目标流场默认格子边长</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LocalDetourProbeLength</t>
+          <t>FlowFieldMinCellSize</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>本地绕行探测长度</t>
+          <t>流场最小格宽</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LocalDetour L/R probe length</t>
+          <t>FlowField min cell size</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>左右绕行探测射线长度</t>
+          <t>流场格宽下限（性能降级时可抬高）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LocalDetourSoftSeparationStrength</t>
+          <t>FlowFieldMaxCellSize</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>本地绕行软分离强度</t>
+          <t>流场最大格宽</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LocalDetour soft separation strength</t>
+          <t>FlowField max cell size</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>友军软分离推力强度</t>
+          <t>流场格宽上限</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LocalDetourDetourBias</t>
+          <t>MassMoveMaxRecalcPerFrame</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>本地绕行偏置</t>
+          <t>群体移动每帧重算上限</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0.85</v>
+        <v>50</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LocalDetour L/R bias blend</t>
+          <t>MassMove/AttackSlot refresh budget per frame</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>绕行方向与原期望方向的混合偏置</t>
+          <t>每帧最多重算路径/攻击位的单位数</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LocalDetourForwardConeHalfAngleDeg</t>
+          <t>MassMoveDefaultAgentRadius</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>本地绕行前向锥半角</t>
+          <t>群体移动默认体半径</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>50</v>
+        <v>0.1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Forward block cone half-angle degrees</t>
+          <t>Default mass-move agent radius</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>判定前方友军阻挡的圆锥半角（度）</t>
+          <t>群体移动登记时的默认体半径</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BossAdvanceArriveRadius</t>
+          <t>MassMoveArriveEpsilon</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Boss推进到达半径</t>
+          <t>群体移动到达阈值</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BossPoint advance arrive radius</t>
+          <t>Arrive epsilon for DesiredDestination</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>目标链耗尽后推进Boss点的到达半径</t>
+          <t>到达期望点判定的距离阈值</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EngageStickHysteresisMargin</t>
+          <t>MassMoveDefaultObjectiveArriveRadius</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>接战粘滞余量</t>
+          <t>目标到达默认半径</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Engage sticky retarget hysteresis</t>
+          <t>Default Objective arrive radius</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
+          <t>目标点到达半径默认值（可被CaptureZone覆盖）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetSeconds</t>
+          <t>MassMoveAttackSlotSeparationScale</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>追击卡住换目标秒数</t>
+          <t>攻击位软分离系数</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chase out-of-range stuck force-retarget window seconds</t>
+          <t>LocalDetour separation scale in AttackSlot</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
+          <t>处于攻击位气泡时LocalDetour软分离缩放</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ChaseStuckRetargetCooldownSeconds</t>
+          <t>SoftCollisionMaxCorrectionSpeed</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>追击卡住换目标冷却</t>
+          <t>软碰撞最大修正速度</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cooldown after chase-stuck force retarget</t>
+          <t>Soft collision max correction speed</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>强制换目标后冷却，防A↔B来回甩</t>
+          <t>软碰撞位置修正速度上限（单位/秒）</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PushMapSpawnMinSampleDistance</t>
+          <t>LocalDetourProbeLength</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>刷怪散布最小采样距</t>
+          <t>本地绕行探测长度</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PushMap spawn min sample distance</t>
+          <t>LocalDetour L/R probe length</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>刷怪散布环形采样的最小间距</t>
+          <t>左右绕行探测射线长度</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PushMapSpawnSampleDistanceBodyMul</t>
+          <t>LocalDetourSoftSeparationStrength</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>刷怪散布体半径倍数</t>
+          <t>本地绕行软分离强度</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Spawn sample distance = max(min</t>
+          <t>LocalDetour soft separation strength</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>友军软分离推力强度</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PushMapSpawnLeashSlack</t>
+          <t>LocalDetourDetourBias</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>刷怪拴绳松弛</t>
+          <t>本地绕行偏置</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NavMesh sample leash slack</t>
+          <t>LocalDetour L/R bias blend</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
+          <t>绕行方向与原期望方向的混合偏置</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashFloor</t>
+          <t>LocalDetourForwardConeHalfAngleDeg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳下限</t>
+          <t>本地绕行前向锥半角</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Absolute leash floor</t>
+          <t>Forward block cone half-angle degrees</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳距离下限</t>
+          <t>判定前方友军阻挡的圆锥半角（度）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
+          <t>BossAdvanceArriveRadius</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>刷怪绝对拴绳体倍数</t>
+          <t>Boss推进到达半径</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>10</v>
+        <v>0.35</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Absolute leash = max(floor</t>
+          <t>BossPoint advance arrive radius</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>r*mul)</t>
+          <t>目标链耗尽后推进Boss点的到达半径</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeathKnockbackRatioCoeff</t>
+          <t>EngageStickHysteresisMargin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>死亡击飞比例系数</t>
+          <t>接战粘滞余量</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
+          <t>Engage sticky retarget hysteresis</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
+          <t>接战粘滞：新目标需更近超过本余量才换目标</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DeathKnockbackMinDistance</t>
+          <t>ChaseStuckRetargetSeconds</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>死亡击飞最小距离</t>
+          <t>追击卡住换目标秒数</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Death knockback distance floor</t>
+          <t>Chase out-of-range stuck force-retarget window seconds</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离下限（世界单位）</t>
+          <t>追击未进距且位移不足达本秒→强制换目标（排除当前/绕过粘滞）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DeathKnockbackMaxDistance</t>
+          <t>ChaseStuckRetargetCooldownSeconds</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>死亡击飞最大距离</t>
+          <t>追击卡住换目标冷却</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Death knockback distance ceiling</t>
+          <t>Cooldown after chase-stuck force retarget</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
+          <t>强制换目标后冷却，防A↔B来回甩</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DeathDie2KnockbackThreshold</t>
+          <t>PushMapSpawnMinSampleDistance</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>死亡Die2击退阈值</t>
+          <t>刷怪散布最小采样距</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
+          <t>PushMap spawn min sample distance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
+          <t>刷怪散布环形采样的最小间距</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
+          <t>PushMapSpawnSampleDistanceBodyMul</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>死亡击飞方向半角扩散</t>
+          <t>刷怪散布体半径倍数</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Max yaw offset each side from base knockback direction (degrees)</t>
+          <t>Spawn sample distance = max(min</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DeathKnockbackDirectionRandomStepDegrees</t>
+          <t>PushMapSpawnLeashSlack</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>死亡击飞方向随机步进</t>
+          <t>刷怪拴绳松弛</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>5</v>
+        <v>0.35</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
+          <t>NavMesh sample leash slack</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
+          <t>刷怪SamplePosition相对基点的拴绳松弛</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DeathKnockbackPeakHeight</t>
+          <t>PushMapSpawnAbsoluteLeashFloor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>死亡击飞抛物线峰值高度</t>
+          <t>刷怪绝对拴绳下限</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Corpse projectile Y arc peak (world units)</t>
+          <t>Absolute leash floor</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
+          <t>刷怪绝对拴绳距离下限</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashDamageMul</t>
+          <t>PushMapSpawnAbsoluteLeashBodyMul</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>尸体砸击伤害系数</t>
+          <t>刷怪绝对拴绳体倍数</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
+          <t>Absolute leash = max(floor</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
+          <t>r*mul)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DeathCorpseSmashHitRadius</t>
+          <t>DeathKnockbackRatioCoeff</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>尸体砸击命中半径</t>
+          <t>死亡击飞比例系数</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0.55</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>In-flight/landing soft-hit radius</t>
+          <t>Knockback raw=(MaxHp/OutgoingDamage)*Coeff</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
+          <t>击飞距离raw=(OutgoingDamage/MaxHp)×本系数；再clamp到Min/Max</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DeathKnockbackSeconds</t>
+          <t>DeathKnockbackMinDistance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>死亡击飞时长</t>
+          <t>死亡击飞最小距离</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Corpse projectile parabolic duration (seconds)</t>
+          <t>Death knockback distance floor</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>尸体投射抛物线时长（秒；与t∈[0</t>
+          <t>怪物死亡击飞距离下限（世界单位）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowAlphaMul</t>
+          <t>DeathKnockbackMaxDistance</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影透明度</t>
+          <t>死亡击飞最大距离</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
+          <t>Death knockback distance ceiling</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
+          <t>怪物死亡击飞距离上限；伤害或MaxHp&lt;=0时用本值</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowScaleMin</t>
+          <t>DeathDie2KnockbackThreshold</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影最小缩放</t>
+          <t>死亡Die2击退阈值</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Min shadow diameter scale at ground height (0-1)</t>
+          <t>Default Die2; knockback distance&gt;=threshold plays Die; else Die2 (no Die2 falls back to Die)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
+          <t>默认Die2；击飞distance&gt;=本值时播Die；否则Die2（无Die2回退Die）</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DeathKnockbackShadowBaseRadiusMul</t>
+          <t>DeathKnockbackDirectionSpreadHalfDegrees</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>击飞腾空地面黑影基准半径倍率</t>
+          <t>死亡击飞方向半角扩散</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
+          <t>Max yaw offset each side from base knockback direction (degrees)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
+          <t>以基准击飞方向为中轴左右各允许的最大偏角（度）；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DeathDefendCorpseAlphaMul</t>
+          <t>DeathKnockbackDirectionRandomStepDegrees</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Defend尸体透明度系数</t>
+          <t>死亡击飞方向随机步进</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.85</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Defend corpse sprite alpha multiplier</t>
+          <t>Knockback yaw random granularity (degrees); offset=k*step</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Defend怪/士兵尸体透明度×本值</t>
+          <t>击飞偏角随机粒度（度）；offset=k×本值；&lt;=0关闭随机</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DeathCorpseDarkenMul</t>
+          <t>DeathKnockbackPeakHeight</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>尸体变暗系数</t>
+          <t>死亡击飞抛物线峰值高度</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Permanent-death corpse RGB multiplier</t>
+          <t>Corpse projectile Y arc peak (world units)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
+          <t>尸体投射Y弧峰值（世界单位；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DeathFakeDeathCorpseDarkenMul</t>
+          <t>DeathCorpseSmashDamageMul</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>假死尸体变暗系数</t>
+          <t>尸体砸击伤害系数</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PushMap fake-death corpse RGB multiplier</t>
+          <t>CorpseSmashDamage = killerOutgoingDamage × this</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PushMap假死尸体RGB×本值</t>
+          <t>尸体砸击伤害=致命击OutgoingDamage×本值（§15.5/D-083）</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScalePerHit</t>
+          <t>DeathCorpseSmashHitRadius</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>士兵命中体型步进</t>
+          <t>尸体砸击命中半径</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
+          <t>In-flight/landing soft-hit radius</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
+          <t>飞行/落地软碰撞半径；缺省对齐ProjectileDefaultHitRadius</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WarriorVisualModelScaleMax</t>
+          <t>DeathKnockbackSeconds</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>士兵模型缩放上限</t>
+          <t>死亡击飞时长</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>12</v>
+        <v>0.8</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
+          <t>Corpse projectile parabolic duration (seconds)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>VisualModelScale每次命中apply末尾夹紧上限</t>
+          <t>尸体投射抛物线时长（秒；与t∈[0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AutoMfgBodyDropIntervalSeconds</t>
+          <t>DeathKnockbackShadowAlphaMul</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>自动制造尸骸落下间隔</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+          <t>击飞腾空地面黑影透明度</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Seconds between body-rain drop batches</t>
+          <t>Ground shadow alpha during corpse parabolic flight (0-1)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UI-016 StepA：每批次掉落间隔秒</t>
+          <t>尸体抛物线腾空阶段地面黑影alpha（0~1；§15.5）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AutoMfgDropCountMin</t>
+          <t>DeathKnockbackShadowScaleMin</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>自动制造尸骸每批最少</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>击飞腾空地面黑影最小缩放</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Min pieces per drop batch</t>
+          <t>Min shadow diameter scale at ground height (0-1)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>StepA 每间隔随机落下件数下限</t>
+          <t>离地时黑影直径相对满缩放的最小系数（0~1；随高度lerp至1）</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AutoMfgDropCountMax</t>
+          <t>DeathKnockbackShadowBaseRadiusMul</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>自动制造尸骸每批最多</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>击飞腾空地面黑影基准半径倍率</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Max pieces per drop batch</t>
+          <t>At peak height: diameter=BodyRadius×2×this×scaleMul</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>StepA 每间隔随机落下件数上限</t>
+          <t>峰值高度时黑影直径=BodyRadius×2×本值×scaleMul</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AutoMfgGravityScale</t>
+          <t>DeathDefendCorpseAlphaMul</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>自动制造尸骸重力</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Defend尸体透明度系数</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0.85</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Rigidbody2D gravityScale for body pieces</t>
+          <t>Defend corpse sprite alpha multiplier</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rigidbody2D.gravityScale</t>
+          <t>Defend怪/士兵尸体透明度×本值</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AutoMfgBounciness</t>
+          <t>DeathCorpseDarkenMul</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>自动制造尸骸弹性</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+          <t>尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0.4</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PhysicsMaterial2D bounciness</t>
+          <t>Permanent-death corpse RGB multiplier</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PhysicsMaterial2D.bounciness</t>
+          <t>彻底死亡/PushMap士兵尸体RGB×本值</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AutoMfgFriction</t>
+          <t>DeathFakeDeathCorpseDarkenMul</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>自动制造尸骸摩擦</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+          <t>假死尸体变暗系数</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0.7</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PhysicsMaterial2D friction</t>
+          <t>PushMap fake-death corpse RGB multiplier</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PhysicsMaterial2D.friction</t>
+          <t>PushMap假死尸体RGB×本值</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AutoMfgColliderInset</t>
+          <t>WarriorVisualModelScalePerHit</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>自动制造尸骸碰撞内缩</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>0.72</v>
+          <t>士兵命中体型步进</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
+          <t>Mode2 MagicBook token hit: VisualModelScale *= this (stackable)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
+          <t>Mode2魔法书Token命中时VisualModelScale乘以本值（可叠；夹Max）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AutoMfgSpawnAngleMaxDeg</t>
+          <t>WarriorVisualModelScaleMax</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>自动制造尸骸落下转角</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>50</v>
+          <t>士兵模型缩放上限</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
+          <t>Clamp VisualModelScale at end of each MagicBook hit apply</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
+          <t>VisualModelScale每次命中apply末尾夹紧上限</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AutoMfgSpawnJitterXPx</t>
+          <t>AutoMfgBodyDropIntervalSeconds</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>自动制造尸骸水平微扰</t>
+          <t>自动制造尸骸落下间隔</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Random spawn X jitter in ref pixels</t>
+          <t>Seconds between body-rain drop batches</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>落点相对屏幕中心 X 微扰</t>
+          <t>UI-016 StepA：每批次掉落间隔秒</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AutoMfgMagicCircleFlashHz</t>
+          <t>AutoMfgDropCountMin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>自动制造法阵闪红频率</t>
+          <t>自动制造尸骸每批最少</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Magic circle red flash Hz during StepB</t>
+          <t>Min pieces per drop batch</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>StepB 法阵红色闪烁 Hz</t>
+          <t>StepA 每间隔随机落下件数下限</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AutoMfgReviveSpawnOffsetYPx</t>
+          <t>AutoMfgDropCountMax</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>自动制造复活出生上偏移</t>
+          <t>自动制造尸骸每批最多</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Revive spawn Y offset from pile base px</t>
+          <t>Max pieces per drop batch</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>问号/士兵出生相对堆底向上像素</t>
+          <t>StepA 每间隔随机落下件数上限</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AutoMfgPileFloorYPx</t>
+          <t>AutoMfgGravityScale</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>自动制造尸骸堆地板 Y</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>-300</v>
+          <t>自动制造尸骸重力</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Body pile floor Y in ref pixels</t>
+          <t>Rigidbody2D gravityScale for body pieces</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2D 演出层堆地板相对屏幕中心 Y</t>
+          <t>Rigidbody2D.gravityScale</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierLandYPx</t>
+          <t>AutoMfgBounciness</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>自动制造士兵落地 Y</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>-410</v>
+          <t>自动制造尸骸弹性</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Revived soldier idle land Y px</t>
+          <t>PhysicsMaterial2D bounciness</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>复活士兵落地相对屏幕中心 Y</t>
+          <t>PhysicsMaterial2D.bounciness</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AutoMfgBodyMaxEdgePx</t>
+          <t>AutoMfgFriction</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>自动制造躯体适配边长</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>49</v>
+          <t>自动制造尸骸摩擦</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>StepA body Image max edge px (~35% of prior 140)</t>
+          <t>PhysicsMaterial2D friction</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+          <t>PhysicsMaterial2D.friction</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierMaxEdgePx</t>
+          <t>AutoMfgColliderInset</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>自动制造士兵固定边长</t>
+          <t>自动制造尸骸碰撞内缩</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>64</v>
+        <v>0.45</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+          <t>OBB edge vs fitted sprite size (&lt;1 lets slanted pieces nest)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+          <t>OBB 边长相对 Sprite 适配尺寸的比例（&lt;1 使斜角更紧）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowWidthPx</t>
+          <t>AutoMfgSpawnAngleMaxDeg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>自动制造士兵影子宽</t>
+          <t>自动制造尸骸落下转角</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Oval foot-shadow width ref px</t>
+          <t>Max abs spawn Z yaw (deg); also scales initial angular velocity</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>复活件脚下椭圆影子宽（参考像素）</t>
+          <t>落下随机 Z 转角绝对值上限（度）；并作初始角速度尺度</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowHeightPx</t>
+          <t>AutoMfgSpawnJitterXPx</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>自动制造士兵影子高</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>8</v>
+          <t>自动制造尸骸水平微扰</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Oval foot-shadow height ref px</t>
+          <t>Random spawn X jitter in ref pixels</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>复活件脚下椭圆影子高（参考像素）</t>
+          <t>落点相对屏幕中心 X 微扰</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowAlpha</t>
+          <t>AutoMfgMagicCircleFlashHz</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>自动制造士兵影子透明度</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>0.45</v>
+          <t>自动制造法阵闪红频率</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Foot-shadow black Alpha 0-1</t>
+          <t>Magic circle red flash Hz during StepB</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>脚下影子黑色 Alpha（0～1）</t>
+          <t>StepB 法阵红色闪烁 Hz</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AutoMfgUseLegacySoldierRow</t>
+          <t>AutoMfgMagicCircleYPx</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>自动制造旧士兵行开关</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>自动制造法阵本地 Y</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>-50</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1=legacy SoldierScroll conveyor</t>
+          <t>MagicCircle anchoredPosition.y vs AmBodyRainLayer</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+          <t>MagicCircle 相对 AmBodyRainLayer 的 anchoredPosition.y</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierVisualScale</t>
+          <t>AutoMfgBodyRainLayerYPx</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>自动制造士兵视觉缩放</t>
+          <t>自动制造尸骸雨层本地 Y</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>-340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Revive piece localScale XYZ</t>
+          <t>AmBodyRainLayer anchoredPosition.y vs PresentationRoot</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>复活件 localScale（XYZ）</t>
+          <t>AmBodyRainLayer 相对 PresentationRoot 的 anchoredPosition.y</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowOffsetYPx</t>
+          <t>AutoMfgReviveSpawnOffsetYPx</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>自动制造士兵影子相对 Y</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>-40</v>
+          <t>自动制造复活出生上偏移</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>400</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Shadow local Y vs soldier center</t>
+          <t>Revive spawn Y offset from pile base px</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>影子相对士兵中心的本地 Y</t>
+          <t>问号/士兵出生相对堆底向上像素</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>AutoMfgPileFloorYPx</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>自动制造尸骸堆地板 Y</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Body pile floor Y in ref pixels</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2D 演出层堆地板相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierLandYPx</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>自动制造士兵落地 Y</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Revived soldier idle land Y px</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>复活士兵落地相对屏幕中心 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>自动制造躯体适配边长</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>49</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>StepA body Image max edge px (~35% of prior 140)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>StepA 躯体 Image 最长边像素（约原 140 的 35%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierMaxEdgePx</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>自动制造士兵固定边长</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>64</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>StepB mystery/soldier Image sizeDelta W/H</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>StepB 问号/士兵 Image sizeDelta 宽高（再 × VisualScale）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowWidthPx</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子宽</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>20</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow width ref px</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子宽（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowHeightPx</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子高</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Oval foot-shadow height ref px</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>复活件脚下椭圆影子高（参考像素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowAlpha</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子透明度</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Foot-shadow black Alpha 0-1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>脚下影子黑色 Alpha（0～1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AutoMfgUseLegacySoldierRow</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>自动制造旧士兵行开关</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1=legacy SoldierScroll conveyor</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1=显示中央传送带旧流程；0=尸骸雨默认</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierVisualScale</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>自动制造士兵视觉缩放</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>8</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Revive piece localScale XYZ</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>复活件 localScale（XYZ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>AutoMfgBodyAngleMaxDeg</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>自动制造躯体绝对转角上限</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="C123" t="n">
         <v>270</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Clamp body Z angle abs deg; zero omega at limit</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" min="1" max="1"/>
@@ -4035,16 +4035,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Foot-shadow black Alpha 0-1</t>
+          <t>Foot-shadow black Alpha 0-1; 0=Demo hide</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>脚下影子黑色 Alpha（0～1）</t>
+          <t>脚下影子黑色 Alpha（0～1；0=Demo 隐藏）</t>
         </is>
       </c>
     </row>
@@ -4103,48 +4103,73 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AutoMfgSoldierShadowOffsetYPx</t>
+          <t>AutoMfgSoldierPitchFactor</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>自动制造士兵影子相对 Y</t>
+          <t>自动制造士兵行间距系数</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-32</v>
+        <v>0.5</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+          <t>StepB row pitch = MaxEdge x VisualScale x Factor</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+          <t>StepB 行间距=MaxEdge×VisualScale×本值（样例0.5→256）</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>AutoMfgSoldierShadowOffsetYPx</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>自动制造士兵影子相对 Y</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Shadow local Y vs soldier feet (bottom pivot)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>影子相对士兵脚底（底部 pivot）的本地 Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>AutoMfgBodyAngleMaxDeg</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>自动制造躯体绝对转角上限</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="C124" t="n">
         <v>270</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Clamp body Z angle abs deg; zero omega at limit</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>躯体 Z 转角夹紧 ±本值；触限清角速度</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" min="1" max="1"/>
@@ -4175,6 +4175,81 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbStaggerSeconds</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入起飞间隔</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>StepB body absorb stagger launch seconds</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>StepB 同兵躯体件错开起飞间隔（秒；随 speed 缩短）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbFlySeconds</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入飞入时长</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>StepB body absorb fly-to-center seconds</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>StepB 单件飞入谜底视觉中心时长（秒；随 speed 缩短）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AutoMfgBodyAbsorbFlashHz</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>自动制造躯体吸入闪红频率</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>8</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>StepB body absorb in-flight white-red flash Hz</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>StepB 飞入中 Image 白↔红闪烁 Hz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
